--- a/swimmer.xlsx
+++ b/swimmer.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="500">
   <si>
     <t>임꺽정</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,9 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>8611</t>
-  </si>
-  <si>
     <t>5168</t>
   </si>
   <si>
@@ -1537,6 +1534,16 @@
   </si>
   <si>
     <t>2849</t>
+  </si>
+  <si>
+    <t>5166</t>
+  </si>
+  <si>
+    <t>5167</t>
+  </si>
+  <si>
+    <t>손흥민</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1588,7 +1595,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1600,9 +1607,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1904,8 +1908,14 @@
     <col min="1" max="1" width="5.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.375" customWidth="1"/>
     <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="11" width="0.5" customWidth="1"/>
+    <col min="4" max="4" width="4.5" customWidth="1"/>
+    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.375" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.625" bestFit="1" customWidth="1"/>
@@ -1979,8 +1989,8 @@
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="L2" s="4">
-        <v>7715</v>
+      <c r="L2" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="M2" s="2">
         <v>0.26041666666666669</v>
@@ -2002,7 +2012,7 @@
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E61" ca="1" si="1">IF(RAND()&gt;0.5, "남자", "여자")</f>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H3">
         <v>5000</v>
@@ -2017,7 +2027,7 @@
         <v>2</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>29</v>
+        <v>498</v>
       </c>
       <c r="M3" s="2">
         <v>0.26041666666666669</v>
@@ -2039,7 +2049,7 @@
       </c>
       <c r="E4" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H4">
         <v>5000</v>
@@ -2054,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M4" s="2">
         <v>0.26041666666666702</v>
@@ -2070,9 +2080,8 @@
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>어우동_1_1_4</v>
+      <c r="C5" t="s">
+        <v>499</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -2091,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M5" s="2">
         <v>0.26041666666666702</v>
@@ -2113,7 +2122,7 @@
       </c>
       <c r="E6" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H6">
         <v>5000</v>
@@ -2128,7 +2137,7 @@
         <v>5</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6" s="2">
         <v>0.26041666666666702</v>
@@ -2165,7 +2174,7 @@
         <v>6</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M7" s="2">
         <v>0.26041666666666702</v>
@@ -2187,7 +2196,7 @@
       </c>
       <c r="E8" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H8">
         <v>5000</v>
@@ -2202,7 +2211,7 @@
         <v>7</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M8" s="2">
         <v>0.26041666666666702</v>
@@ -2239,7 +2248,7 @@
         <v>8</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" s="2">
         <v>0.26041666666666702</v>
@@ -2276,7 +2285,7 @@
         <v>9</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M10" s="2">
         <v>0.26041666666666702</v>
@@ -2313,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M11" s="2">
         <v>0.26041666666666702</v>
@@ -2335,7 +2344,7 @@
       </c>
       <c r="E12" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H12">
         <v>5000</v>
@@ -2350,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M12" s="2">
         <v>0.26041666666666702</v>
@@ -2387,7 +2396,7 @@
         <v>2</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2">
         <v>0.26041666666666702</v>
@@ -2424,7 +2433,7 @@
         <v>3</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M14" s="2">
         <v>0.26041666666666702</v>
@@ -2446,7 +2455,7 @@
       </c>
       <c r="E15" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H15">
         <v>5000</v>
@@ -2461,7 +2470,7 @@
         <v>4</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M15" s="2">
         <v>0.26041666666666702</v>
@@ -2483,7 +2492,7 @@
       </c>
       <c r="E16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H16">
         <v>5000</v>
@@ -2498,7 +2507,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M16" s="2">
         <v>0.26041666666666702</v>
@@ -2520,7 +2529,7 @@
       </c>
       <c r="E17" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H17">
         <v>5000</v>
@@ -2535,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M17" s="2">
         <v>0.26041666666666702</v>
@@ -2557,7 +2566,7 @@
       </c>
       <c r="E18" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H18">
         <v>5000</v>
@@ -2572,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M18" s="2">
         <v>0.26041666666666702</v>
@@ -2594,7 +2603,7 @@
       </c>
       <c r="E19" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H19">
         <v>5000</v>
@@ -2609,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2">
         <v>0.26041666666666702</v>
@@ -2646,7 +2655,7 @@
         <v>9</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M20" s="2">
         <v>0.26041666666666702</v>
@@ -2683,7 +2692,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M21" s="2">
         <v>0.26041666666666702</v>
@@ -2705,7 +2714,7 @@
       </c>
       <c r="E22" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H22">
         <v>5000</v>
@@ -2720,7 +2729,7 @@
         <v>11</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M22" s="2">
         <v>0.26041666666666702</v>
@@ -2757,7 +2766,7 @@
         <v>12</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M23" s="2">
         <v>0.26041666666666702</v>
@@ -2794,7 +2803,7 @@
         <v>13</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M24" s="2">
         <v>0.26041666666666702</v>
@@ -2831,7 +2840,7 @@
         <v>14</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M25" s="2">
         <v>0.26041666666666702</v>
@@ -2853,7 +2862,7 @@
       </c>
       <c r="E26" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H26">
         <v>5000</v>
@@ -2868,7 +2877,7 @@
         <v>15</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2">
         <v>0.26041666666666702</v>
@@ -2905,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M27" s="2">
         <v>0.26041666666666702</v>
@@ -2942,7 +2951,7 @@
         <v>2</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M28" s="2">
         <v>0.26041666666666702</v>
@@ -2964,7 +2973,7 @@
       </c>
       <c r="E29" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H29">
         <v>5000</v>
@@ -2979,7 +2988,7 @@
         <v>3</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M29" s="2">
         <v>0.26041666666666702</v>
@@ -3001,7 +3010,7 @@
       </c>
       <c r="E30" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H30">
         <v>5000</v>
@@ -3016,7 +3025,7 @@
         <v>4</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M30" s="2">
         <v>0.26041666666666702</v>
@@ -3038,7 +3047,7 @@
       </c>
       <c r="E31" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H31">
         <v>5000</v>
@@ -3053,7 +3062,7 @@
         <v>5</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M31" s="2">
         <v>0.26041666666666702</v>
@@ -3075,7 +3084,7 @@
       </c>
       <c r="E32" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H32">
         <v>5000</v>
@@ -3090,7 +3099,7 @@
         <v>6</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M32" s="2">
         <v>0.26041666666666702</v>
@@ -3112,7 +3121,7 @@
       </c>
       <c r="E33" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H33">
         <v>5000</v>
@@ -3127,7 +3136,7 @@
         <v>7</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M33" s="2">
         <v>0.26041666666666702</v>
@@ -3149,7 +3158,7 @@
       </c>
       <c r="E34" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H34">
         <v>5000</v>
@@ -3164,7 +3173,7 @@
         <v>8</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M34" s="2">
         <v>0.26041666666666702</v>
@@ -3201,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M35" s="2">
         <v>0.26041666666666702</v>
@@ -3223,7 +3232,7 @@
       </c>
       <c r="E36" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H36">
         <v>5000</v>
@@ -3238,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M36" s="2">
         <v>0.26041666666666702</v>
@@ -3260,7 +3269,7 @@
       </c>
       <c r="E37" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H37">
         <v>5000</v>
@@ -3275,7 +3284,7 @@
         <v>11</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M37" s="2">
         <v>0.26041666666666702</v>
@@ -3297,7 +3306,7 @@
       </c>
       <c r="E38" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H38">
         <v>5000</v>
@@ -3312,7 +3321,7 @@
         <v>12</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M38" s="2">
         <v>0.26041666666666702</v>
@@ -3349,7 +3358,7 @@
         <v>13</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M39" s="2">
         <v>0.26041666666666702</v>
@@ -3371,7 +3380,7 @@
       </c>
       <c r="E40" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H40">
         <v>5000</v>
@@ -3386,7 +3395,7 @@
         <v>14</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M40" s="2">
         <v>0.26041666666666702</v>
@@ -3423,7 +3432,7 @@
         <v>15</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M41" s="2">
         <v>0.26041666666666702</v>
@@ -3460,7 +3469,7 @@
         <v>1</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M42" s="2">
         <v>0.26041666666666702</v>
@@ -3482,7 +3491,7 @@
       </c>
       <c r="E43" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H43">
         <v>5000</v>
@@ -3497,7 +3506,7 @@
         <v>2</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M43" s="2">
         <v>0.26041666666666702</v>
@@ -3519,7 +3528,7 @@
       </c>
       <c r="E44" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H44">
         <v>5000</v>
@@ -3534,7 +3543,7 @@
         <v>3</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M44" s="2">
         <v>0.26041666666666702</v>
@@ -3556,7 +3565,7 @@
       </c>
       <c r="E45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H45">
         <v>5000</v>
@@ -3571,7 +3580,7 @@
         <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M45" s="2">
         <v>0.26041666666666702</v>
@@ -3593,7 +3602,7 @@
       </c>
       <c r="E46" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H46">
         <v>5000</v>
@@ -3608,7 +3617,7 @@
         <v>5</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M46" s="2">
         <v>0.26041666666666702</v>
@@ -3645,7 +3654,7 @@
         <v>6</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M47" s="2">
         <v>0.26041666666666702</v>
@@ -3667,7 +3676,7 @@
       </c>
       <c r="E48" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H48">
         <v>5000</v>
@@ -3682,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M48" s="2">
         <v>0.26041666666666702</v>
@@ -3719,7 +3728,7 @@
         <v>8</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M49" s="2">
         <v>0.26041666666666702</v>
@@ -3741,7 +3750,7 @@
       </c>
       <c r="E50" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H50">
         <v>5000</v>
@@ -3756,7 +3765,7 @@
         <v>9</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M50" s="2">
         <v>0.26041666666666702</v>
@@ -3793,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M51" s="2">
         <v>0.26041666666666702</v>
@@ -3830,7 +3839,7 @@
         <v>11</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M52" s="2">
         <v>0.26041666666666702</v>
@@ -3852,7 +3861,7 @@
       </c>
       <c r="E53" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H53">
         <v>5000</v>
@@ -3867,7 +3876,7 @@
         <v>12</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M53" s="2">
         <v>0.26041666666666702</v>
@@ -3904,7 +3913,7 @@
         <v>13</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M54" s="2">
         <v>0.26041666666666702</v>
@@ -3941,7 +3950,7 @@
         <v>14</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M55" s="2">
         <v>0.26041666666666702</v>
@@ -3978,7 +3987,7 @@
         <v>15</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M56" s="2">
         <v>0.26041666666666702</v>
@@ -4015,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M57" s="2">
         <v>0.26041666666666702</v>
@@ -4037,7 +4046,7 @@
       </c>
       <c r="E58" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H58">
         <v>5000</v>
@@ -4052,7 +4061,7 @@
         <v>2</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M58" s="2">
         <v>0.26041666666666702</v>
@@ -4074,7 +4083,7 @@
       </c>
       <c r="E59" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H59">
         <v>5000</v>
@@ -4089,7 +4098,7 @@
         <v>3</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M59" s="2">
         <v>0.26041666666666702</v>
@@ -4126,7 +4135,7 @@
         <v>4</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M60" s="2">
         <v>0.26041666666666702</v>
@@ -4163,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M61" s="2">
         <v>0.26041666666666702</v>
@@ -4185,7 +4194,7 @@
       </c>
       <c r="E62" t="str">
         <f t="shared" ref="E62:E125" ca="1" si="2">IF(RAND()&gt;0.5, "남자", "여자")</f>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H62">
         <v>5000</v>
@@ -4200,7 +4209,7 @@
         <v>6</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M62" s="2">
         <v>0.26041666666666702</v>
@@ -4237,7 +4246,7 @@
         <v>7</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M63" s="2">
         <v>0.26041666666666702</v>
@@ -4259,7 +4268,7 @@
       </c>
       <c r="E64" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H64">
         <v>5000</v>
@@ -4274,7 +4283,7 @@
         <v>8</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M64" s="2">
         <v>0.26041666666666702</v>
@@ -4311,7 +4320,7 @@
         <v>9</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M65" s="2">
         <v>0.26041666666666702</v>
@@ -4333,7 +4342,7 @@
       </c>
       <c r="E66" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H66">
         <v>5000</v>
@@ -4348,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M66" s="2">
         <v>0.26041666666666702</v>
@@ -4370,7 +4379,7 @@
       </c>
       <c r="E67" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H67">
         <v>5000</v>
@@ -4385,7 +4394,7 @@
         <v>11</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M67" s="2">
         <v>0.26041666666666702</v>
@@ -4422,7 +4431,7 @@
         <v>12</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M68" s="2">
         <v>0.26041666666666702</v>
@@ -4459,7 +4468,7 @@
         <v>13</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M69" s="2">
         <v>0.26041666666666702</v>
@@ -4496,7 +4505,7 @@
         <v>14</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M70" s="2">
         <v>0.26041666666666702</v>
@@ -4518,7 +4527,7 @@
       </c>
       <c r="E71" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H71">
         <v>5000</v>
@@ -4533,7 +4542,7 @@
         <v>15</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M71" s="2">
         <v>0.26041666666666702</v>
@@ -4555,7 +4564,7 @@
       </c>
       <c r="E72" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H72">
         <v>5000</v>
@@ -4570,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M72" s="2">
         <v>0.26041666666666702</v>
@@ -4607,7 +4616,7 @@
         <v>2</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M73" s="2">
         <v>0.26041666666666702</v>
@@ -4644,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M74" s="2">
         <v>0.26041666666666702</v>
@@ -4666,7 +4675,7 @@
       </c>
       <c r="E75" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H75">
         <v>5000</v>
@@ -4681,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M75" s="2">
         <v>0.26041666666666702</v>
@@ -4703,7 +4712,7 @@
       </c>
       <c r="E76" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H76">
         <v>5000</v>
@@ -4718,7 +4727,7 @@
         <v>5</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M76" s="2">
         <v>0.26041666666666702</v>
@@ -4755,7 +4764,7 @@
         <v>6</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M77" s="2">
         <v>0.26041666666666702</v>
@@ -4792,7 +4801,7 @@
         <v>7</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M78" s="2">
         <v>0.26041666666666702</v>
@@ -4829,7 +4838,7 @@
         <v>8</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M79" s="2">
         <v>0.26041666666666702</v>
@@ -4851,7 +4860,7 @@
       </c>
       <c r="E80" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H80">
         <v>5000</v>
@@ -4866,7 +4875,7 @@
         <v>9</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M80" s="2">
         <v>0.26041666666666702</v>
@@ -4903,7 +4912,7 @@
         <v>10</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M81" s="2">
         <v>0.26041666666666702</v>
@@ -4925,7 +4934,7 @@
       </c>
       <c r="E82" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H82">
         <v>5000</v>
@@ -4940,7 +4949,7 @@
         <v>11</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M82" s="2">
         <v>0.26041666666666702</v>
@@ -4962,7 +4971,7 @@
       </c>
       <c r="E83" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H83">
         <v>5000</v>
@@ -4977,7 +4986,7 @@
         <v>12</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M83" s="2">
         <v>0.26041666666666702</v>
@@ -5014,7 +5023,7 @@
         <v>13</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M84" s="2">
         <v>0.26041666666666702</v>
@@ -5051,7 +5060,7 @@
         <v>14</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M85" s="2">
         <v>0.26041666666666702</v>
@@ -5073,7 +5082,7 @@
       </c>
       <c r="E86" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H86">
         <v>5000</v>
@@ -5088,7 +5097,7 @@
         <v>15</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M86" s="2">
         <v>0.26041666666666702</v>
@@ -5125,7 +5134,7 @@
         <v>1</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M87" s="2">
         <v>0.26041666666666702</v>
@@ -5162,7 +5171,7 @@
         <v>2</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M88" s="2">
         <v>0.26041666666666702</v>
@@ -5184,7 +5193,7 @@
       </c>
       <c r="E89" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H89">
         <v>5000</v>
@@ -5199,7 +5208,7 @@
         <v>3</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M89" s="2">
         <v>0.26041666666666702</v>
@@ -5236,7 +5245,7 @@
         <v>4</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M90" s="2">
         <v>0.26041666666666702</v>
@@ -5273,7 +5282,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M91" s="2">
         <v>0.26041666666666702</v>
@@ -5310,7 +5319,7 @@
         <v>6</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M92" s="2">
         <v>0.26041666666666702</v>
@@ -5332,7 +5341,7 @@
       </c>
       <c r="E93" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H93">
         <v>5000</v>
@@ -5347,7 +5356,7 @@
         <v>7</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M93" s="2">
         <v>0.26041666666666702</v>
@@ -5369,7 +5378,7 @@
       </c>
       <c r="E94" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H94">
         <v>5000</v>
@@ -5384,7 +5393,7 @@
         <v>8</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M94" s="2">
         <v>0.26041666666666702</v>
@@ -5421,7 +5430,7 @@
         <v>9</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M95" s="2">
         <v>0.26041666666666702</v>
@@ -5458,7 +5467,7 @@
         <v>10</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M96" s="2">
         <v>0.26041666666666702</v>
@@ -5495,7 +5504,7 @@
         <v>11</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M97" s="2">
         <v>0.26041666666666702</v>
@@ -5532,7 +5541,7 @@
         <v>12</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M98" s="2">
         <v>0.26041666666666702</v>
@@ -5569,7 +5578,7 @@
         <v>13</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M99" s="2">
         <v>0.26041666666666702</v>
@@ -5591,7 +5600,7 @@
       </c>
       <c r="E100" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H100">
         <v>5000</v>
@@ -5606,7 +5615,7 @@
         <v>14</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M100" s="2">
         <v>0.26041666666666702</v>
@@ -5643,7 +5652,7 @@
         <v>15</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M101" s="2">
         <v>0.26041666666666702</v>
@@ -5680,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M102" s="2">
         <v>0.26041666666666702</v>
@@ -5702,7 +5711,7 @@
       </c>
       <c r="E103" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H103">
         <v>5000</v>
@@ -5717,7 +5726,7 @@
         <v>2</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M103" s="2">
         <v>0.26041666666666702</v>
@@ -5754,7 +5763,7 @@
         <v>3</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M104" s="2">
         <v>0.26041666666666702</v>
@@ -5776,7 +5785,7 @@
       </c>
       <c r="E105" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H105">
         <v>5000</v>
@@ -5791,7 +5800,7 @@
         <v>4</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M105" s="2">
         <v>0.26041666666666702</v>
@@ -5813,7 +5822,7 @@
       </c>
       <c r="E106" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H106">
         <v>5000</v>
@@ -5828,7 +5837,7 @@
         <v>5</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M106" s="2">
         <v>0.26041666666666702</v>
@@ -5850,7 +5859,7 @@
       </c>
       <c r="E107" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H107">
         <v>5000</v>
@@ -5865,7 +5874,7 @@
         <v>6</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M107" s="2">
         <v>0.26041666666666702</v>
@@ -5887,7 +5896,7 @@
       </c>
       <c r="E108" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H108">
         <v>5000</v>
@@ -5902,7 +5911,7 @@
         <v>7</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M108" s="2">
         <v>0.26041666666666702</v>
@@ -5924,7 +5933,7 @@
       </c>
       <c r="E109" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H109">
         <v>5000</v>
@@ -5939,7 +5948,7 @@
         <v>8</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M109" s="2">
         <v>0.26041666666666702</v>
@@ -5976,7 +5985,7 @@
         <v>9</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M110" s="2">
         <v>0.26041666666666702</v>
@@ -5998,7 +6007,7 @@
       </c>
       <c r="E111" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H111">
         <v>5000</v>
@@ -6013,7 +6022,7 @@
         <v>10</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M111" s="2">
         <v>0.26041666666666702</v>
@@ -6050,7 +6059,7 @@
         <v>11</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M112" s="2">
         <v>0.26041666666666702</v>
@@ -6072,7 +6081,7 @@
       </c>
       <c r="E113" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H113">
         <v>5000</v>
@@ -6087,7 +6096,7 @@
         <v>12</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M113" s="2">
         <v>0.26041666666666702</v>
@@ -6124,7 +6133,7 @@
         <v>13</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M114" s="2">
         <v>0.26041666666666702</v>
@@ -6146,7 +6155,7 @@
       </c>
       <c r="E115" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H115">
         <v>5000</v>
@@ -6161,7 +6170,7 @@
         <v>14</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M115" s="2">
         <v>0.26041666666666702</v>
@@ -6183,7 +6192,7 @@
       </c>
       <c r="E116" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H116">
         <v>5000</v>
@@ -6198,7 +6207,7 @@
         <v>15</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M116" s="2">
         <v>0.26041666666666702</v>
@@ -6220,7 +6229,7 @@
       </c>
       <c r="E117" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H117">
         <v>5000</v>
@@ -6235,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M117" s="2">
         <v>0.33333333333333331</v>
@@ -6272,7 +6281,7 @@
         <v>2</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M118" s="2">
         <v>0.33333333333333331</v>
@@ -6309,7 +6318,7 @@
         <v>3</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M119" s="2">
         <v>0.33333333333333298</v>
@@ -6346,7 +6355,7 @@
         <v>4</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M120" s="2">
         <v>0.33333333333333298</v>
@@ -6383,7 +6392,7 @@
         <v>5</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M121" s="2">
         <v>0.33333333333333298</v>
@@ -6420,7 +6429,7 @@
         <v>6</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M122" s="2">
         <v>0.33333333333333298</v>
@@ -6442,7 +6451,7 @@
       </c>
       <c r="E123" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H123">
         <v>5000</v>
@@ -6457,7 +6466,7 @@
         <v>7</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M123" s="2">
         <v>0.33333333333333298</v>
@@ -6479,7 +6488,7 @@
       </c>
       <c r="E124" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H124">
         <v>5000</v>
@@ -6494,7 +6503,7 @@
         <v>8</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M124" s="2">
         <v>0.33333333333333298</v>
@@ -6516,7 +6525,7 @@
       </c>
       <c r="E125" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H125">
         <v>5000</v>
@@ -6531,7 +6540,7 @@
         <v>9</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M125" s="2">
         <v>0.33333333333333298</v>
@@ -6553,7 +6562,7 @@
       </c>
       <c r="E126" t="str">
         <f t="shared" ref="E126:E189" ca="1" si="4">IF(RAND()&gt;0.5, "남자", "여자")</f>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H126">
         <v>5000</v>
@@ -6568,7 +6577,7 @@
         <v>10</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M126" s="2">
         <v>0.33333333333333298</v>
@@ -6605,7 +6614,7 @@
         <v>11</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M127" s="2">
         <v>0.33333333333333298</v>
@@ -6642,7 +6651,7 @@
         <v>12</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M128" s="2">
         <v>0.33333333333333298</v>
@@ -6664,7 +6673,7 @@
       </c>
       <c r="E129" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H129">
         <v>5000</v>
@@ -6679,7 +6688,7 @@
         <v>13</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M129" s="2">
         <v>0.33333333333333298</v>
@@ -6701,7 +6710,7 @@
       </c>
       <c r="E130" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H130">
         <v>5000</v>
@@ -6716,7 +6725,7 @@
         <v>14</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M130" s="2">
         <v>0.33333333333333298</v>
@@ -6738,7 +6747,7 @@
       </c>
       <c r="E131" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H131">
         <v>5000</v>
@@ -6753,7 +6762,7 @@
         <v>15</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M131" s="2">
         <v>0.33333333333333298</v>
@@ -6775,7 +6784,7 @@
       </c>
       <c r="E132" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H132">
         <v>5000</v>
@@ -6790,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M132" s="2">
         <v>0.33333333333333298</v>
@@ -6827,7 +6836,7 @@
         <v>2</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M133" s="2">
         <v>0.33333333333333298</v>
@@ -6864,7 +6873,7 @@
         <v>3</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M134" s="2">
         <v>0.33333333333333298</v>
@@ -6901,7 +6910,7 @@
         <v>4</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M135" s="2">
         <v>0.33333333333333298</v>
@@ -6923,7 +6932,7 @@
       </c>
       <c r="E136" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H136">
         <v>5000</v>
@@ -6938,7 +6947,7 @@
         <v>5</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M136" s="2">
         <v>0.33333333333333298</v>
@@ -6975,7 +6984,7 @@
         <v>6</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M137" s="2">
         <v>0.33333333333333298</v>
@@ -6997,7 +7006,7 @@
       </c>
       <c r="E138" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H138">
         <v>5000</v>
@@ -7012,7 +7021,7 @@
         <v>7</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M138" s="2">
         <v>0.33333333333333298</v>
@@ -7049,7 +7058,7 @@
         <v>8</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M139" s="2">
         <v>0.33333333333333298</v>
@@ -7071,7 +7080,7 @@
       </c>
       <c r="E140" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H140">
         <v>5000</v>
@@ -7086,7 +7095,7 @@
         <v>9</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M140" s="2">
         <v>0.33333333333333298</v>
@@ -7123,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M141" s="2">
         <v>0.33333333333333298</v>
@@ -7145,7 +7154,7 @@
       </c>
       <c r="E142" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H142">
         <v>5000</v>
@@ -7160,7 +7169,7 @@
         <v>11</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M142" s="2">
         <v>0.33333333333333298</v>
@@ -7197,7 +7206,7 @@
         <v>12</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M143" s="2">
         <v>0.33333333333333298</v>
@@ -7219,7 +7228,7 @@
       </c>
       <c r="E144" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H144">
         <v>5000</v>
@@ -7234,7 +7243,7 @@
         <v>13</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M144" s="2">
         <v>0.33333333333333298</v>
@@ -7256,7 +7265,7 @@
       </c>
       <c r="E145" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H145">
         <v>5000</v>
@@ -7271,7 +7280,7 @@
         <v>14</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M145" s="2">
         <v>0.33333333333333298</v>
@@ -7293,7 +7302,7 @@
       </c>
       <c r="E146" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H146">
         <v>5000</v>
@@ -7308,7 +7317,7 @@
         <v>15</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M146" s="2">
         <v>0.33333333333333298</v>
@@ -7345,7 +7354,7 @@
         <v>1</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M147" s="2">
         <v>0.33333333333333298</v>
@@ -7367,7 +7376,7 @@
       </c>
       <c r="E148" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H148">
         <v>5000</v>
@@ -7382,7 +7391,7 @@
         <v>2</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M148" s="2">
         <v>0.33333333333333298</v>
@@ -7404,7 +7413,7 @@
       </c>
       <c r="E149" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H149">
         <v>5000</v>
@@ -7419,7 +7428,7 @@
         <v>3</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M149" s="2">
         <v>0.33333333333333298</v>
@@ -7456,7 +7465,7 @@
         <v>4</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M150" s="2">
         <v>0.33333333333333298</v>
@@ -7493,7 +7502,7 @@
         <v>5</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M151" s="2">
         <v>0.33333333333333298</v>
@@ -7530,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M152" s="2">
         <v>0.33333333333333298</v>
@@ -7552,7 +7561,7 @@
       </c>
       <c r="E153" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H153">
         <v>5000</v>
@@ -7567,7 +7576,7 @@
         <v>7</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M153" s="2">
         <v>0.33333333333333298</v>
@@ -7589,7 +7598,7 @@
       </c>
       <c r="E154" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H154">
         <v>5000</v>
@@ -7604,7 +7613,7 @@
         <v>8</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M154" s="2">
         <v>0.33333333333333298</v>
@@ -7641,7 +7650,7 @@
         <v>9</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M155" s="2">
         <v>0.33333333333333298</v>
@@ -7678,7 +7687,7 @@
         <v>10</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M156" s="2">
         <v>0.33333333333333298</v>
@@ -7700,7 +7709,7 @@
       </c>
       <c r="E157" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H157">
         <v>5000</v>
@@ -7715,7 +7724,7 @@
         <v>11</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M157" s="2">
         <v>0.33333333333333298</v>
@@ -7752,7 +7761,7 @@
         <v>12</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M158" s="2">
         <v>0.33333333333333298</v>
@@ -7789,7 +7798,7 @@
         <v>13</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M159" s="2">
         <v>0.33333333333333298</v>
@@ -7811,7 +7820,7 @@
       </c>
       <c r="E160" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H160">
         <v>5000</v>
@@ -7826,7 +7835,7 @@
         <v>14</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M160" s="2">
         <v>0.33333333333333298</v>
@@ -7863,7 +7872,7 @@
         <v>15</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M161" s="2">
         <v>0.33333333333333298</v>
@@ -7900,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M162" s="2">
         <v>0.33333333333333298</v>
@@ -7937,7 +7946,7 @@
         <v>2</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M163" s="2">
         <v>0.33333333333333298</v>
@@ -7974,7 +7983,7 @@
         <v>3</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M164" s="2">
         <v>0.33333333333333298</v>
@@ -8011,7 +8020,7 @@
         <v>4</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M165" s="2">
         <v>0.33333333333333298</v>
@@ -8033,7 +8042,7 @@
       </c>
       <c r="E166" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H166">
         <v>5000</v>
@@ -8048,7 +8057,7 @@
         <v>5</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M166" s="2">
         <v>0.33333333333333298</v>
@@ -8070,7 +8079,7 @@
       </c>
       <c r="E167" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H167">
         <v>5000</v>
@@ -8085,7 +8094,7 @@
         <v>6</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M167" s="2">
         <v>0.33333333333333298</v>
@@ -8122,7 +8131,7 @@
         <v>7</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M168" s="2">
         <v>0.33333333333333298</v>
@@ -8144,7 +8153,7 @@
       </c>
       <c r="E169" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H169">
         <v>5000</v>
@@ -8159,7 +8168,7 @@
         <v>8</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M169" s="2">
         <v>0.33333333333333298</v>
@@ -8196,7 +8205,7 @@
         <v>9</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M170" s="2">
         <v>0.33333333333333298</v>
@@ -8233,7 +8242,7 @@
         <v>10</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M171" s="2">
         <v>0.33333333333333298</v>
@@ -8255,7 +8264,7 @@
       </c>
       <c r="E172" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H172">
         <v>5000</v>
@@ -8270,7 +8279,7 @@
         <v>11</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M172" s="2">
         <v>0.33333333333333298</v>
@@ -8292,7 +8301,7 @@
       </c>
       <c r="E173" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H173">
         <v>5000</v>
@@ -8307,7 +8316,7 @@
         <v>12</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M173" s="2">
         <v>0.33333333333333298</v>
@@ -8329,7 +8338,7 @@
       </c>
       <c r="E174" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H174">
         <v>5000</v>
@@ -8344,7 +8353,7 @@
         <v>13</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M174" s="2">
         <v>0.33333333333333298</v>
@@ -8381,7 +8390,7 @@
         <v>14</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M175" s="2">
         <v>0.33333333333333298</v>
@@ -8418,7 +8427,7 @@
         <v>15</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M176" s="2">
         <v>0.33333333333333298</v>
@@ -8440,7 +8449,7 @@
       </c>
       <c r="E177" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H177">
         <v>5000</v>
@@ -8455,7 +8464,7 @@
         <v>1</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M177" s="2">
         <v>0.33333333333333298</v>
@@ -8492,7 +8501,7 @@
         <v>2</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="M178" s="2">
         <v>0.33333333333333298</v>
@@ -8514,7 +8523,7 @@
       </c>
       <c r="E179" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H179">
         <v>5000</v>
@@ -8529,7 +8538,7 @@
         <v>3</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M179" s="2">
         <v>0.33333333333333298</v>
@@ -8551,7 +8560,7 @@
       </c>
       <c r="E180" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H180">
         <v>5000</v>
@@ -8566,7 +8575,7 @@
         <v>4</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M180" s="2">
         <v>0.33333333333333298</v>
@@ -8588,7 +8597,7 @@
       </c>
       <c r="E181" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H181">
         <v>5000</v>
@@ -8603,7 +8612,7 @@
         <v>5</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M181" s="2">
         <v>0.33333333333333298</v>
@@ -8625,7 +8634,7 @@
       </c>
       <c r="E182" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H182">
         <v>5000</v>
@@ -8640,7 +8649,7 @@
         <v>6</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M182" s="2">
         <v>0.33333333333333298</v>
@@ -8662,7 +8671,7 @@
       </c>
       <c r="E183" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H183">
         <v>5000</v>
@@ -8677,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M183" s="2">
         <v>0.33333333333333298</v>
@@ -8714,7 +8723,7 @@
         <v>8</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="M184" s="2">
         <v>0.33333333333333298</v>
@@ -8751,7 +8760,7 @@
         <v>9</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M185" s="2">
         <v>0.33333333333333298</v>
@@ -8788,7 +8797,7 @@
         <v>10</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M186" s="2">
         <v>0.33333333333333298</v>
@@ -8825,7 +8834,7 @@
         <v>11</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M187" s="2">
         <v>0.33333333333333298</v>
@@ -8847,7 +8856,7 @@
       </c>
       <c r="E188" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H188">
         <v>5000</v>
@@ -8862,7 +8871,7 @@
         <v>12</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M188" s="2">
         <v>0.33333333333333298</v>
@@ -8884,7 +8893,7 @@
       </c>
       <c r="E189" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H189">
         <v>5000</v>
@@ -8899,7 +8908,7 @@
         <v>13</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M189" s="2">
         <v>0.33333333333333298</v>
@@ -8936,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M190" s="2">
         <v>0.33333333333333298</v>
@@ -8958,7 +8967,7 @@
       </c>
       <c r="E191" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H191">
         <v>5000</v>
@@ -8973,7 +8982,7 @@
         <v>15</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M191" s="2">
         <v>0.33333333333333298</v>
@@ -8995,7 +9004,7 @@
       </c>
       <c r="E192" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H192">
         <v>5000</v>
@@ -9010,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M192" s="2">
         <v>0.33333333333333298</v>
@@ -9047,7 +9056,7 @@
         <v>2</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M193" s="2">
         <v>0.33333333333333298</v>
@@ -9069,7 +9078,7 @@
       </c>
       <c r="E194" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H194">
         <v>5000</v>
@@ -9084,7 +9093,7 @@
         <v>3</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M194" s="2">
         <v>0.33333333333333298</v>
@@ -9106,7 +9115,7 @@
       </c>
       <c r="E195" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H195">
         <v>5000</v>
@@ -9121,7 +9130,7 @@
         <v>4</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M195" s="2">
         <v>0.33333333333333298</v>
@@ -9143,7 +9152,7 @@
       </c>
       <c r="E196" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H196">
         <v>5000</v>
@@ -9158,7 +9167,7 @@
         <v>5</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M196" s="2">
         <v>0.33333333333333298</v>
@@ -9195,7 +9204,7 @@
         <v>6</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="M197" s="2">
         <v>0.33333333333333298</v>
@@ -9217,7 +9226,7 @@
       </c>
       <c r="E198" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H198">
         <v>5000</v>
@@ -9232,7 +9241,7 @@
         <v>7</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="M198" s="2">
         <v>0.33333333333333298</v>
@@ -9269,7 +9278,7 @@
         <v>8</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M199" s="2">
         <v>0.33333333333333298</v>
@@ -9306,7 +9315,7 @@
         <v>9</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M200" s="2">
         <v>0.33333333333333298</v>
@@ -9343,7 +9352,7 @@
         <v>10</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M201" s="2">
         <v>0.33333333333333298</v>
@@ -9365,7 +9374,7 @@
       </c>
       <c r="E202" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H202">
         <v>5000</v>
@@ -9380,7 +9389,7 @@
         <v>11</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M202" s="2">
         <v>0.33333333333333298</v>
@@ -9402,7 +9411,7 @@
       </c>
       <c r="E203" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H203">
         <v>5000</v>
@@ -9417,7 +9426,7 @@
         <v>12</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="M203" s="2">
         <v>0.33333333333333298</v>
@@ -9454,7 +9463,7 @@
         <v>13</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M204" s="2">
         <v>0.33333333333333298</v>
@@ -9491,7 +9500,7 @@
         <v>14</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="M205" s="2">
         <v>0.33333333333333298</v>
@@ -9528,7 +9537,7 @@
         <v>15</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M206" s="2">
         <v>0.33333333333333298</v>
@@ -9565,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M207" s="2">
         <v>0.33333333333333298</v>
@@ -9602,7 +9611,7 @@
         <v>2</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="M208" s="2">
         <v>0.33333333333333298</v>
@@ -9624,7 +9633,7 @@
       </c>
       <c r="E209" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H209">
         <v>5000</v>
@@ -9639,7 +9648,7 @@
         <v>3</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="M209" s="2">
         <v>0.33333333333333298</v>
@@ -9676,7 +9685,7 @@
         <v>4</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M210" s="2">
         <v>0.33333333333333298</v>
@@ -9698,7 +9707,7 @@
       </c>
       <c r="E211" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H211">
         <v>5000</v>
@@ -9713,7 +9722,7 @@
         <v>5</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M211" s="2">
         <v>0.33333333333333298</v>
@@ -9750,7 +9759,7 @@
         <v>6</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="M212" s="2">
         <v>0.33333333333333298</v>
@@ -9772,7 +9781,7 @@
       </c>
       <c r="E213" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H213">
         <v>5000</v>
@@ -9787,7 +9796,7 @@
         <v>7</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M213" s="2">
         <v>0.33333333333333298</v>
@@ -9809,7 +9818,7 @@
       </c>
       <c r="E214" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H214">
         <v>5000</v>
@@ -9824,7 +9833,7 @@
         <v>8</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M214" s="2">
         <v>0.33333333333333298</v>
@@ -9861,7 +9870,7 @@
         <v>9</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="M215" s="2">
         <v>0.33333333333333298</v>
@@ -9898,7 +9907,7 @@
         <v>10</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M216" s="2">
         <v>0.33333333333333298</v>
@@ -9935,7 +9944,7 @@
         <v>11</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="M217" s="2">
         <v>0.33333333333333298</v>
@@ -9972,7 +9981,7 @@
         <v>12</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M218" s="2">
         <v>0.33333333333333298</v>
@@ -10009,7 +10018,7 @@
         <v>13</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M219" s="2">
         <v>0.33333333333333298</v>
@@ -10031,7 +10040,7 @@
       </c>
       <c r="E220" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H220">
         <v>5000</v>
@@ -10046,7 +10055,7 @@
         <v>14</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="M220" s="2">
         <v>0.33333333333333298</v>
@@ -10068,7 +10077,7 @@
       </c>
       <c r="E221" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H221">
         <v>5000</v>
@@ -10083,7 +10092,7 @@
         <v>15</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="M221" s="2">
         <v>0.33333333333333298</v>
@@ -10120,7 +10129,7 @@
         <v>1</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M222" s="2">
         <v>0.33333333333333298</v>
@@ -10142,7 +10151,7 @@
       </c>
       <c r="E223" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H223">
         <v>5000</v>
@@ -10157,7 +10166,7 @@
         <v>2</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="M223" s="2">
         <v>0.33333333333333298</v>
@@ -10179,7 +10188,7 @@
       </c>
       <c r="E224" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H224">
         <v>5000</v>
@@ -10194,7 +10203,7 @@
         <v>3</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M224" s="2">
         <v>0.33333333333333298</v>
@@ -10216,7 +10225,7 @@
       </c>
       <c r="E225" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H225">
         <v>5000</v>
@@ -10231,7 +10240,7 @@
         <v>4</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M225" s="2">
         <v>0.33333333333333298</v>
@@ -10268,7 +10277,7 @@
         <v>5</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M226" s="2">
         <v>0.33333333333333298</v>
@@ -10305,7 +10314,7 @@
         <v>6</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M227" s="2">
         <v>0.33333333333333298</v>
@@ -10327,7 +10336,7 @@
       </c>
       <c r="E228" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H228">
         <v>5000</v>
@@ -10342,7 +10351,7 @@
         <v>7</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M228" s="2">
         <v>0.33333333333333298</v>
@@ -10364,7 +10373,7 @@
       </c>
       <c r="E229" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H229">
         <v>5000</v>
@@ -10379,7 +10388,7 @@
         <v>8</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M229" s="2">
         <v>0.33333333333333298</v>
@@ -10416,7 +10425,7 @@
         <v>9</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M230" s="2">
         <v>0.33333333333333298</v>
@@ -10453,7 +10462,7 @@
         <v>10</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M231" s="2">
         <v>0.33333333333333298</v>
@@ -10490,7 +10499,7 @@
         <v>11</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M232" s="2">
         <v>0.33333333333333298</v>
@@ -10512,7 +10521,7 @@
       </c>
       <c r="E233" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H233">
         <v>5000</v>
@@ -10527,7 +10536,7 @@
         <v>12</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M233" s="2">
         <v>0.33333333333333298</v>
@@ -10549,7 +10558,7 @@
       </c>
       <c r="E234" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H234">
         <v>5000</v>
@@ -10564,7 +10573,7 @@
         <v>13</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M234" s="2">
         <v>0.33333333333333298</v>
@@ -10601,7 +10610,7 @@
         <v>14</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M235" s="2">
         <v>0.33333333333333298</v>
@@ -10623,7 +10632,7 @@
       </c>
       <c r="E236" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H236">
         <v>5000</v>
@@ -10638,7 +10647,7 @@
         <v>15</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M236" s="2">
         <v>0.33333333333333298</v>
@@ -10660,7 +10669,7 @@
       </c>
       <c r="E237" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H237">
         <v>10000</v>
@@ -10675,7 +10684,7 @@
         <v>1</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M237" s="2">
         <v>0.4236111111111111</v>
@@ -10712,7 +10721,7 @@
         <v>2</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M238" s="2">
         <v>0.4236111111111111</v>
@@ -10749,7 +10758,7 @@
         <v>3</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M239" s="2">
         <v>0.42361111111111099</v>
@@ -10786,7 +10795,7 @@
         <v>4</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M240" s="2">
         <v>0.42361111111111099</v>
@@ -10823,7 +10832,7 @@
         <v>5</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M241" s="2">
         <v>0.42361111111111099</v>
@@ -10845,7 +10854,7 @@
       </c>
       <c r="E242" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H242">
         <v>10000</v>
@@ -10860,7 +10869,7 @@
         <v>6</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M242" s="2">
         <v>0.42361111111111099</v>
@@ -10882,7 +10891,7 @@
       </c>
       <c r="E243" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H243">
         <v>10000</v>
@@ -10897,7 +10906,7 @@
         <v>7</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M243" s="2">
         <v>0.42361111111111099</v>
@@ -10919,7 +10928,7 @@
       </c>
       <c r="E244" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H244">
         <v>10000</v>
@@ -10934,7 +10943,7 @@
         <v>8</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M244" s="2">
         <v>0.42361111111111099</v>
@@ -10971,7 +10980,7 @@
         <v>9</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M245" s="2">
         <v>0.42361111111111099</v>
@@ -10993,7 +11002,7 @@
       </c>
       <c r="E246" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H246">
         <v>10000</v>
@@ -11008,7 +11017,7 @@
         <v>10</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M246" s="2">
         <v>0.42361111111111099</v>
@@ -11045,7 +11054,7 @@
         <v>11</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M247" s="2">
         <v>0.42361111111111099</v>
@@ -11082,7 +11091,7 @@
         <v>12</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M248" s="2">
         <v>0.42361111111111099</v>
@@ -11104,7 +11113,7 @@
       </c>
       <c r="E249" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H249">
         <v>10000</v>
@@ -11119,7 +11128,7 @@
         <v>13</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M249" s="2">
         <v>0.42361111111111099</v>
@@ -11141,7 +11150,7 @@
       </c>
       <c r="E250" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H250">
         <v>10000</v>
@@ -11156,7 +11165,7 @@
         <v>14</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M250" s="2">
         <v>0.42361111111111099</v>
@@ -11178,7 +11187,7 @@
       </c>
       <c r="E251" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H251">
         <v>10000</v>
@@ -11193,7 +11202,7 @@
         <v>15</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M251" s="2">
         <v>0.42361111111111099</v>
@@ -11215,7 +11224,7 @@
       </c>
       <c r="E252" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H252">
         <v>10000</v>
@@ -11230,7 +11239,7 @@
         <v>1</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M252" s="2">
         <v>0.42361111111111099</v>
@@ -11267,7 +11276,7 @@
         <v>2</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M253" s="2">
         <v>0.42361111111111099</v>
@@ -11304,7 +11313,7 @@
         <v>3</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M254" s="2">
         <v>0.42361111111111099</v>
@@ -11341,7 +11350,7 @@
         <v>4</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M255" s="2">
         <v>0.42361111111111099</v>
@@ -11378,7 +11387,7 @@
         <v>5</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M256" s="2">
         <v>0.42361111111111099</v>
@@ -11400,7 +11409,7 @@
       </c>
       <c r="E257" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H257">
         <v>10000</v>
@@ -11415,7 +11424,7 @@
         <v>6</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M257" s="2">
         <v>0.42361111111111099</v>
@@ -11437,7 +11446,7 @@
       </c>
       <c r="E258" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H258">
         <v>10000</v>
@@ -11452,7 +11461,7 @@
         <v>7</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M258" s="2">
         <v>0.42361111111111099</v>
@@ -11474,7 +11483,7 @@
       </c>
       <c r="E259" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H259">
         <v>10000</v>
@@ -11489,7 +11498,7 @@
         <v>8</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M259" s="2">
         <v>0.42361111111111099</v>
@@ -11511,7 +11520,7 @@
       </c>
       <c r="E260" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H260">
         <v>10000</v>
@@ -11526,7 +11535,7 @@
         <v>9</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M260" s="2">
         <v>0.42361111111111099</v>
@@ -11548,7 +11557,7 @@
       </c>
       <c r="E261" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H261">
         <v>10000</v>
@@ -11563,7 +11572,7 @@
         <v>10</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M261" s="2">
         <v>0.42361111111111099</v>
@@ -11585,7 +11594,7 @@
       </c>
       <c r="E262" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H262">
         <v>10000</v>
@@ -11600,7 +11609,7 @@
         <v>11</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M262" s="2">
         <v>0.42361111111111099</v>
@@ -11637,7 +11646,7 @@
         <v>12</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M263" s="2">
         <v>0.42361111111111099</v>
@@ -11659,7 +11668,7 @@
       </c>
       <c r="E264" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H264">
         <v>10000</v>
@@ -11674,7 +11683,7 @@
         <v>13</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M264" s="2">
         <v>0.42361111111111099</v>
@@ -11696,7 +11705,7 @@
       </c>
       <c r="E265" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H265">
         <v>10000</v>
@@ -11711,7 +11720,7 @@
         <v>14</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M265" s="2">
         <v>0.42361111111111099</v>
@@ -11733,7 +11742,7 @@
       </c>
       <c r="E266" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H266">
         <v>10000</v>
@@ -11748,7 +11757,7 @@
         <v>15</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M266" s="2">
         <v>0.42361111111111099</v>
@@ -11785,7 +11794,7 @@
         <v>1</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="M267" s="2">
         <v>0.42361111111111099</v>
@@ -11807,7 +11816,7 @@
       </c>
       <c r="E268" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H268">
         <v>10000</v>
@@ -11822,7 +11831,7 @@
         <v>2</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M268" s="2">
         <v>0.42361111111111099</v>
@@ -11859,7 +11868,7 @@
         <v>3</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M269" s="2">
         <v>0.42361111111111099</v>
@@ -11896,7 +11905,7 @@
         <v>4</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M270" s="2">
         <v>0.42361111111111099</v>
@@ -11918,7 +11927,7 @@
       </c>
       <c r="E271" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H271">
         <v>10000</v>
@@ -11933,7 +11942,7 @@
         <v>5</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M271" s="2">
         <v>0.42361111111111099</v>
@@ -11955,7 +11964,7 @@
       </c>
       <c r="E272" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H272">
         <v>10000</v>
@@ -11970,7 +11979,7 @@
         <v>6</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M272" s="2">
         <v>0.42361111111111099</v>
@@ -11992,7 +12001,7 @@
       </c>
       <c r="E273" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H273">
         <v>10000</v>
@@ -12007,7 +12016,7 @@
         <v>7</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="M273" s="2">
         <v>0.42361111111111099</v>
@@ -12029,7 +12038,7 @@
       </c>
       <c r="E274" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H274">
         <v>10000</v>
@@ -12044,7 +12053,7 @@
         <v>8</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M274" s="2">
         <v>0.42361111111111099</v>
@@ -12066,7 +12075,7 @@
       </c>
       <c r="E275" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H275">
         <v>10000</v>
@@ -12081,7 +12090,7 @@
         <v>9</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M275" s="2">
         <v>0.42361111111111099</v>
@@ -12118,7 +12127,7 @@
         <v>10</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M276" s="2">
         <v>0.42361111111111099</v>
@@ -12155,7 +12164,7 @@
         <v>11</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M277" s="2">
         <v>0.42361111111111099</v>
@@ -12192,7 +12201,7 @@
         <v>12</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M278" s="2">
         <v>0.42361111111111099</v>
@@ -12214,7 +12223,7 @@
       </c>
       <c r="E279" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H279">
         <v>10000</v>
@@ -12229,7 +12238,7 @@
         <v>13</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M279" s="2">
         <v>0.42361111111111099</v>
@@ -12251,7 +12260,7 @@
       </c>
       <c r="E280" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H280">
         <v>10000</v>
@@ -12266,7 +12275,7 @@
         <v>14</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M280" s="2">
         <v>0.42361111111111099</v>
@@ -12303,7 +12312,7 @@
         <v>15</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M281" s="2">
         <v>0.42361111111111099</v>
@@ -12325,7 +12334,7 @@
       </c>
       <c r="E282" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H282">
         <v>10000</v>
@@ -12340,7 +12349,7 @@
         <v>1</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M282" s="2">
         <v>0.42361111111111099</v>
@@ -12377,7 +12386,7 @@
         <v>2</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M283" s="2">
         <v>0.42361111111111099</v>
@@ -12414,7 +12423,7 @@
         <v>3</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M284" s="2">
         <v>0.42361111111111099</v>
@@ -12451,7 +12460,7 @@
         <v>4</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M285" s="2">
         <v>0.42361111111111099</v>
@@ -12488,7 +12497,7 @@
         <v>5</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M286" s="2">
         <v>0.42361111111111099</v>
@@ -12510,7 +12519,7 @@
       </c>
       <c r="E287" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H287">
         <v>10000</v>
@@ -12525,7 +12534,7 @@
         <v>6</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M287" s="2">
         <v>0.42361111111111099</v>
@@ -12562,7 +12571,7 @@
         <v>7</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M288" s="2">
         <v>0.42361111111111099</v>
@@ -12584,7 +12593,7 @@
       </c>
       <c r="E289" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H289">
         <v>10000</v>
@@ -12599,7 +12608,7 @@
         <v>8</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M289" s="2">
         <v>0.42361111111111099</v>
@@ -12621,7 +12630,7 @@
       </c>
       <c r="E290" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H290">
         <v>10000</v>
@@ -12636,7 +12645,7 @@
         <v>9</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M290" s="2">
         <v>0.42361111111111099</v>
@@ -12673,7 +12682,7 @@
         <v>10</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M291" s="2">
         <v>0.42361111111111099</v>
@@ -12710,7 +12719,7 @@
         <v>11</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M292" s="2">
         <v>0.42361111111111099</v>
@@ -12747,7 +12756,7 @@
         <v>12</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="M293" s="2">
         <v>0.42361111111111099</v>
@@ -12784,7 +12793,7 @@
         <v>13</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M294" s="2">
         <v>0.42361111111111099</v>
@@ -12821,7 +12830,7 @@
         <v>14</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M295" s="2">
         <v>0.42361111111111099</v>
@@ -12858,7 +12867,7 @@
         <v>15</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="M296" s="2">
         <v>0.42361111111111099</v>
@@ -12880,7 +12889,7 @@
       </c>
       <c r="E297" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H297">
         <v>10000</v>
@@ -12895,7 +12904,7 @@
         <v>1</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M297" s="2">
         <v>0.42361111111111099</v>
@@ -12932,7 +12941,7 @@
         <v>2</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M298" s="2">
         <v>0.42361111111111099</v>
@@ -12954,7 +12963,7 @@
       </c>
       <c r="E299" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H299">
         <v>10000</v>
@@ -12969,7 +12978,7 @@
         <v>3</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M299" s="2">
         <v>0.42361111111111099</v>
@@ -12991,7 +13000,7 @@
       </c>
       <c r="E300" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H300">
         <v>10000</v>
@@ -13006,7 +13015,7 @@
         <v>4</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M300" s="2">
         <v>0.42361111111111099</v>
@@ -13028,7 +13037,7 @@
       </c>
       <c r="E301" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H301">
         <v>10000</v>
@@ -13043,7 +13052,7 @@
         <v>5</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M301" s="2">
         <v>0.42361111111111099</v>
@@ -13080,7 +13089,7 @@
         <v>6</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M302" s="2">
         <v>0.42361111111111099</v>
@@ -13102,7 +13111,7 @@
       </c>
       <c r="E303" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H303">
         <v>10000</v>
@@ -13117,7 +13126,7 @@
         <v>7</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M303" s="2">
         <v>0.42361111111111099</v>
@@ -13154,7 +13163,7 @@
         <v>8</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M304" s="2">
         <v>0.42361111111111099</v>
@@ -13191,7 +13200,7 @@
         <v>9</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M305" s="2">
         <v>0.42361111111111099</v>
@@ -13228,7 +13237,7 @@
         <v>10</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M306" s="2">
         <v>0.42361111111111099</v>
@@ -13250,7 +13259,7 @@
       </c>
       <c r="E307" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H307">
         <v>10000</v>
@@ -13265,7 +13274,7 @@
         <v>11</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M307" s="2">
         <v>0.42361111111111099</v>
@@ -13287,7 +13296,7 @@
       </c>
       <c r="E308" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H308">
         <v>10000</v>
@@ -13302,7 +13311,7 @@
         <v>12</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M308" s="2">
         <v>0.42361111111111099</v>
@@ -13324,7 +13333,7 @@
       </c>
       <c r="E309" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H309">
         <v>10000</v>
@@ -13339,7 +13348,7 @@
         <v>13</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M309" s="2">
         <v>0.42361111111111099</v>
@@ -13361,7 +13370,7 @@
       </c>
       <c r="E310" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H310">
         <v>10000</v>
@@ -13376,7 +13385,7 @@
         <v>14</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M310" s="2">
         <v>0.42361111111111099</v>
@@ -13398,7 +13407,7 @@
       </c>
       <c r="E311" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H311">
         <v>10000</v>
@@ -13413,7 +13422,7 @@
         <v>15</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M311" s="2">
         <v>0.42361111111111099</v>
@@ -13450,7 +13459,7 @@
         <v>1</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M312" s="2">
         <v>0.42361111111111099</v>
@@ -13487,7 +13496,7 @@
         <v>2</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M313" s="2">
         <v>0.42361111111111099</v>
@@ -13524,7 +13533,7 @@
         <v>3</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M314" s="2">
         <v>0.42361111111111099</v>
@@ -13546,7 +13555,7 @@
       </c>
       <c r="E315" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H315">
         <v>10000</v>
@@ -13561,7 +13570,7 @@
         <v>4</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="M315" s="2">
         <v>0.42361111111111099</v>
@@ -13598,7 +13607,7 @@
         <v>5</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M316" s="2">
         <v>0.42361111111111099</v>
@@ -13620,7 +13629,7 @@
       </c>
       <c r="E317" t="str">
         <f t="shared" ca="1" si="8"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H317">
         <v>10000</v>
@@ -13635,7 +13644,7 @@
         <v>6</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M317" s="2">
         <v>0.42361111111111099</v>
@@ -13672,7 +13681,7 @@
         <v>7</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M318" s="2">
         <v>0.42361111111111099</v>
@@ -13694,7 +13703,7 @@
       </c>
       <c r="E319" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H319">
         <v>10000</v>
@@ -13709,7 +13718,7 @@
         <v>8</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="M319" s="2">
         <v>0.42361111111111099</v>
@@ -13731,7 +13740,7 @@
       </c>
       <c r="E320" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H320">
         <v>10000</v>
@@ -13746,7 +13755,7 @@
         <v>9</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M320" s="2">
         <v>0.42361111111111099</v>
@@ -13768,7 +13777,7 @@
       </c>
       <c r="E321" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H321">
         <v>10000</v>
@@ -13783,7 +13792,7 @@
         <v>10</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M321" s="2">
         <v>0.42361111111111099</v>
@@ -13805,7 +13814,7 @@
       </c>
       <c r="E322" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H322">
         <v>10000</v>
@@ -13820,7 +13829,7 @@
         <v>11</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M322" s="2">
         <v>0.42361111111111099</v>
@@ -13842,7 +13851,7 @@
       </c>
       <c r="E323" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H323">
         <v>10000</v>
@@ -13857,7 +13866,7 @@
         <v>12</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M323" s="2">
         <v>0.42361111111111099</v>
@@ -13894,7 +13903,7 @@
         <v>13</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M324" s="2">
         <v>0.42361111111111099</v>
@@ -13931,7 +13940,7 @@
         <v>14</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M325" s="2">
         <v>0.42361111111111099</v>
@@ -13953,7 +13962,7 @@
       </c>
       <c r="E326" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H326">
         <v>10000</v>
@@ -13968,7 +13977,7 @@
         <v>15</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M326" s="2">
         <v>0.42361111111111099</v>
@@ -13990,7 +13999,7 @@
       </c>
       <c r="E327" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H327">
         <v>10000</v>
@@ -14005,7 +14014,7 @@
         <v>1</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M327" s="2">
         <v>0.42361111111111099</v>
@@ -14027,7 +14036,7 @@
       </c>
       <c r="E328" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H328">
         <v>10000</v>
@@ -14042,7 +14051,7 @@
         <v>2</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="M328" s="2">
         <v>0.42361111111111099</v>
@@ -14079,7 +14088,7 @@
         <v>3</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M329" s="2">
         <v>0.42361111111111099</v>
@@ -14116,7 +14125,7 @@
         <v>4</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="M330" s="2">
         <v>0.42361111111111099</v>
@@ -14153,7 +14162,7 @@
         <v>5</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="M331" s="2">
         <v>0.42361111111111099</v>
@@ -14190,7 +14199,7 @@
         <v>6</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M332" s="2">
         <v>0.42361111111111099</v>
@@ -14212,7 +14221,7 @@
       </c>
       <c r="E333" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H333">
         <v>10000</v>
@@ -14227,7 +14236,7 @@
         <v>7</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M333" s="2">
         <v>0.42361111111111099</v>
@@ -14249,7 +14258,7 @@
       </c>
       <c r="E334" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H334">
         <v>10000</v>
@@ -14264,7 +14273,7 @@
         <v>8</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="M334" s="2">
         <v>0.42361111111111099</v>
@@ -14301,7 +14310,7 @@
         <v>9</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M335" s="2">
         <v>0.42361111111111099</v>
@@ -14323,7 +14332,7 @@
       </c>
       <c r="E336" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H336">
         <v>10000</v>
@@ -14338,7 +14347,7 @@
         <v>10</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M336" s="2">
         <v>0.42361111111111099</v>
@@ -14375,7 +14384,7 @@
         <v>11</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="M337" s="2">
         <v>0.42361111111111099</v>
@@ -14397,7 +14406,7 @@
       </c>
       <c r="E338" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H338">
         <v>10000</v>
@@ -14412,7 +14421,7 @@
         <v>12</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M338" s="2">
         <v>0.42361111111111099</v>
@@ -14434,7 +14443,7 @@
       </c>
       <c r="E339" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H339">
         <v>10000</v>
@@ -14449,7 +14458,7 @@
         <v>13</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="M339" s="2">
         <v>0.42361111111111099</v>
@@ -14471,7 +14480,7 @@
       </c>
       <c r="E340" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H340">
         <v>10000</v>
@@ -14486,7 +14495,7 @@
         <v>14</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M340" s="2">
         <v>0.42361111111111099</v>
@@ -14523,7 +14532,7 @@
         <v>15</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M341" s="2">
         <v>0.42361111111111099</v>
@@ -14545,7 +14554,7 @@
       </c>
       <c r="E342" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H342">
         <v>10000</v>
@@ -14560,7 +14569,7 @@
         <v>1</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M342" s="2">
         <v>0.42361111111111099</v>
@@ -14597,7 +14606,7 @@
         <v>2</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="M343" s="2">
         <v>0.42361111111111099</v>
@@ -14619,7 +14628,7 @@
       </c>
       <c r="E344" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H344">
         <v>10000</v>
@@ -14634,7 +14643,7 @@
         <v>3</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="M344" s="2">
         <v>0.42361111111111099</v>
@@ -14671,7 +14680,7 @@
         <v>4</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M345" s="2">
         <v>0.42361111111111099</v>
@@ -14708,7 +14717,7 @@
         <v>5</v>
       </c>
       <c r="L346" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="M346" s="2">
         <v>0.42361111111111099</v>
@@ -14745,7 +14754,7 @@
         <v>6</v>
       </c>
       <c r="L347" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="M347" s="2">
         <v>0.42361111111111099</v>
@@ -14767,7 +14776,7 @@
       </c>
       <c r="E348" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H348">
         <v>10000</v>
@@ -14782,7 +14791,7 @@
         <v>7</v>
       </c>
       <c r="L348" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M348" s="2">
         <v>0.42361111111111099</v>
@@ -14819,7 +14828,7 @@
         <v>8</v>
       </c>
       <c r="L349" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M349" s="2">
         <v>0.42361111111111099</v>
@@ -14841,7 +14850,7 @@
       </c>
       <c r="E350" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H350">
         <v>10000</v>
@@ -14856,7 +14865,7 @@
         <v>9</v>
       </c>
       <c r="L350" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="M350" s="2">
         <v>0.42361111111111099</v>
@@ -14893,7 +14902,7 @@
         <v>10</v>
       </c>
       <c r="L351" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M351" s="2">
         <v>0.42361111111111099</v>
@@ -14930,7 +14939,7 @@
         <v>11</v>
       </c>
       <c r="L352" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="M352" s="2">
         <v>0.42361111111111099</v>
@@ -14967,7 +14976,7 @@
         <v>12</v>
       </c>
       <c r="L353" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="M353" s="2">
         <v>0.42361111111111099</v>
@@ -14989,7 +14998,7 @@
       </c>
       <c r="E354" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H354">
         <v>10000</v>
@@ -15004,7 +15013,7 @@
         <v>13</v>
       </c>
       <c r="L354" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M354" s="2">
         <v>0.42361111111111099</v>
@@ -15041,7 +15050,7 @@
         <v>14</v>
       </c>
       <c r="L355" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M355" s="2">
         <v>0.42361111111111099</v>
@@ -15063,7 +15072,7 @@
       </c>
       <c r="E356" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H356">
         <v>10000</v>
@@ -15078,7 +15087,7 @@
         <v>15</v>
       </c>
       <c r="L356" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="M356" s="2">
         <v>0.42361111111111099</v>
@@ -15115,7 +15124,7 @@
         <v>1</v>
       </c>
       <c r="L357" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="M357" s="2">
         <v>0.60416666666666663</v>
@@ -15137,7 +15146,7 @@
       </c>
       <c r="E358" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H358">
         <v>5000</v>
@@ -15152,7 +15161,7 @@
         <v>2</v>
       </c>
       <c r="L358" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M358" s="2">
         <v>0.60416666666666663</v>
@@ -15189,7 +15198,7 @@
         <v>3</v>
       </c>
       <c r="L359" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M359" s="2">
         <v>0.60416666666666696</v>
@@ -15226,7 +15235,7 @@
         <v>4</v>
       </c>
       <c r="L360" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M360" s="2">
         <v>0.60416666666666696</v>
@@ -15263,7 +15272,7 @@
         <v>5</v>
       </c>
       <c r="L361" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M361" s="2">
         <v>0.60416666666666696</v>
@@ -15300,7 +15309,7 @@
         <v>6</v>
       </c>
       <c r="L362" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M362" s="2">
         <v>0.60416666666666696</v>
@@ -15337,7 +15346,7 @@
         <v>7</v>
       </c>
       <c r="L363" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M363" s="2">
         <v>0.60416666666666696</v>
@@ -15359,7 +15368,7 @@
       </c>
       <c r="E364" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H364">
         <v>5000</v>
@@ -15374,7 +15383,7 @@
         <v>8</v>
       </c>
       <c r="L364" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M364" s="2">
         <v>0.60416666666666696</v>
@@ -15411,7 +15420,7 @@
         <v>9</v>
       </c>
       <c r="L365" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M365" s="2">
         <v>0.60416666666666696</v>
@@ -15433,7 +15442,7 @@
       </c>
       <c r="E366" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H366">
         <v>5000</v>
@@ -15448,7 +15457,7 @@
         <v>10</v>
       </c>
       <c r="L366" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M366" s="2">
         <v>0.60416666666666696</v>
@@ -15470,7 +15479,7 @@
       </c>
       <c r="E367" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H367">
         <v>5000</v>
@@ -15485,7 +15494,7 @@
         <v>11</v>
       </c>
       <c r="L367" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M367" s="2">
         <v>0.60416666666666696</v>
@@ -15507,7 +15516,7 @@
       </c>
       <c r="E368" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H368">
         <v>5000</v>
@@ -15522,7 +15531,7 @@
         <v>12</v>
       </c>
       <c r="L368" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M368" s="2">
         <v>0.60416666666666696</v>
@@ -15544,7 +15553,7 @@
       </c>
       <c r="E369" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H369">
         <v>5000</v>
@@ -15559,7 +15568,7 @@
         <v>13</v>
       </c>
       <c r="L369" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="M369" s="2">
         <v>0.60416666666666696</v>
@@ -15596,7 +15605,7 @@
         <v>14</v>
       </c>
       <c r="L370" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M370" s="2">
         <v>0.60416666666666696</v>
@@ -15618,7 +15627,7 @@
       </c>
       <c r="E371" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H371">
         <v>5000</v>
@@ -15633,7 +15642,7 @@
         <v>15</v>
       </c>
       <c r="L371" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M371" s="2">
         <v>0.60416666666666696</v>
@@ -15670,7 +15679,7 @@
         <v>1</v>
       </c>
       <c r="L372" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M372" s="2">
         <v>0.60416666666666696</v>
@@ -15692,7 +15701,7 @@
       </c>
       <c r="E373" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H373">
         <v>5000</v>
@@ -15707,7 +15716,7 @@
         <v>2</v>
       </c>
       <c r="L373" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="M373" s="2">
         <v>0.60416666666666696</v>
@@ -15744,7 +15753,7 @@
         <v>3</v>
       </c>
       <c r="L374" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M374" s="2">
         <v>0.60416666666666696</v>
@@ -15766,7 +15775,7 @@
       </c>
       <c r="E375" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H375">
         <v>5000</v>
@@ -15781,7 +15790,7 @@
         <v>4</v>
       </c>
       <c r="L375" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="M375" s="2">
         <v>0.60416666666666696</v>
@@ -15803,7 +15812,7 @@
       </c>
       <c r="E376" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H376">
         <v>5000</v>
@@ -15818,7 +15827,7 @@
         <v>5</v>
       </c>
       <c r="L376" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M376" s="2">
         <v>0.60416666666666696</v>
@@ -15855,7 +15864,7 @@
         <v>6</v>
       </c>
       <c r="L377" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M377" s="2">
         <v>0.60416666666666696</v>
@@ -15877,7 +15886,7 @@
       </c>
       <c r="E378" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H378">
         <v>5000</v>
@@ -15892,7 +15901,7 @@
         <v>7</v>
       </c>
       <c r="L378" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M378" s="2">
         <v>0.60416666666666696</v>
@@ -15914,7 +15923,7 @@
       </c>
       <c r="E379" t="str">
         <f t="shared" ca="1" si="10"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H379">
         <v>5000</v>
@@ -15929,7 +15938,7 @@
         <v>8</v>
       </c>
       <c r="L379" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M379" s="2">
         <v>0.60416666666666696</v>
@@ -15966,7 +15975,7 @@
         <v>9</v>
       </c>
       <c r="L380" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M380" s="2">
         <v>0.60416666666666696</v>
@@ -16003,7 +16012,7 @@
         <v>10</v>
       </c>
       <c r="L381" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M381" s="2">
         <v>0.60416666666666696</v>
@@ -16025,7 +16034,7 @@
       </c>
       <c r="E382" t="str">
         <f t="shared" ref="E382:E445" ca="1" si="12">IF(RAND()&gt;0.5, "남자", "여자")</f>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H382">
         <v>5000</v>
@@ -16040,7 +16049,7 @@
         <v>11</v>
       </c>
       <c r="L382" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M382" s="2">
         <v>0.60416666666666696</v>
@@ -16077,7 +16086,7 @@
         <v>12</v>
       </c>
       <c r="L383" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M383" s="2">
         <v>0.60416666666666696</v>
@@ -16099,7 +16108,7 @@
       </c>
       <c r="E384" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H384">
         <v>5000</v>
@@ -16114,7 +16123,7 @@
         <v>13</v>
       </c>
       <c r="L384" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M384" s="2">
         <v>0.60416666666666696</v>
@@ -16136,7 +16145,7 @@
       </c>
       <c r="E385" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H385">
         <v>5000</v>
@@ -16151,7 +16160,7 @@
         <v>14</v>
       </c>
       <c r="L385" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M385" s="2">
         <v>0.60416666666666696</v>
@@ -16173,7 +16182,7 @@
       </c>
       <c r="E386" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H386">
         <v>5000</v>
@@ -16188,7 +16197,7 @@
         <v>15</v>
       </c>
       <c r="L386" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M386" s="2">
         <v>0.60416666666666696</v>
@@ -16225,7 +16234,7 @@
         <v>1</v>
       </c>
       <c r="L387" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M387" s="2">
         <v>0.60416666666666696</v>
@@ -16247,7 +16256,7 @@
       </c>
       <c r="E388" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H388">
         <v>5000</v>
@@ -16262,7 +16271,7 @@
         <v>2</v>
       </c>
       <c r="L388" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M388" s="2">
         <v>0.60416666666666696</v>
@@ -16284,7 +16293,7 @@
       </c>
       <c r="E389" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H389">
         <v>5000</v>
@@ -16299,7 +16308,7 @@
         <v>3</v>
       </c>
       <c r="L389" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M389" s="2">
         <v>0.60416666666666696</v>
@@ -16336,7 +16345,7 @@
         <v>4</v>
       </c>
       <c r="L390" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M390" s="2">
         <v>0.60416666666666696</v>
@@ -16358,7 +16367,7 @@
       </c>
       <c r="E391" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H391">
         <v>5000</v>
@@ -16373,7 +16382,7 @@
         <v>5</v>
       </c>
       <c r="L391" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M391" s="2">
         <v>0.60416666666666696</v>
@@ -16410,7 +16419,7 @@
         <v>6</v>
       </c>
       <c r="L392" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="M392" s="2">
         <v>0.60416666666666696</v>
@@ -16447,7 +16456,7 @@
         <v>7</v>
       </c>
       <c r="L393" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M393" s="2">
         <v>0.60416666666666696</v>
@@ -16469,7 +16478,7 @@
       </c>
       <c r="E394" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H394">
         <v>5000</v>
@@ -16484,7 +16493,7 @@
         <v>8</v>
       </c>
       <c r="L394" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="M394" s="2">
         <v>0.60416666666666696</v>
@@ -16521,7 +16530,7 @@
         <v>9</v>
       </c>
       <c r="L395" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M395" s="2">
         <v>0.60416666666666696</v>
@@ -16543,7 +16552,7 @@
       </c>
       <c r="E396" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H396">
         <v>5000</v>
@@ -16558,7 +16567,7 @@
         <v>10</v>
       </c>
       <c r="L396" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M396" s="2">
         <v>0.60416666666666696</v>
@@ -16595,7 +16604,7 @@
         <v>11</v>
       </c>
       <c r="L397" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M397" s="2">
         <v>0.60416666666666696</v>
@@ -16632,7 +16641,7 @@
         <v>12</v>
       </c>
       <c r="L398" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M398" s="2">
         <v>0.60416666666666696</v>
@@ -16669,7 +16678,7 @@
         <v>13</v>
       </c>
       <c r="L399" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M399" s="2">
         <v>0.60416666666666696</v>
@@ -16691,7 +16700,7 @@
       </c>
       <c r="E400" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H400">
         <v>5000</v>
@@ -16706,7 +16715,7 @@
         <v>14</v>
       </c>
       <c r="L400" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M400" s="2">
         <v>0.60416666666666696</v>
@@ -16728,7 +16737,7 @@
       </c>
       <c r="E401" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H401">
         <v>5000</v>
@@ -16743,7 +16752,7 @@
         <v>15</v>
       </c>
       <c r="L401" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M401" s="2">
         <v>0.60416666666666696</v>
@@ -16765,7 +16774,7 @@
       </c>
       <c r="E402" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H402">
         <v>5000</v>
@@ -16780,7 +16789,7 @@
         <v>1</v>
       </c>
       <c r="L402" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M402" s="2">
         <v>0.60416666666666696</v>
@@ -16817,7 +16826,7 @@
         <v>2</v>
       </c>
       <c r="L403" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M403" s="2">
         <v>0.60416666666666696</v>
@@ -16854,7 +16863,7 @@
         <v>3</v>
       </c>
       <c r="L404" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M404" s="2">
         <v>0.60416666666666696</v>
@@ -16891,7 +16900,7 @@
         <v>4</v>
       </c>
       <c r="L405" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M405" s="2">
         <v>0.60416666666666696</v>
@@ -16928,7 +16937,7 @@
         <v>5</v>
       </c>
       <c r="L406" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M406" s="2">
         <v>0.60416666666666696</v>
@@ -16950,7 +16959,7 @@
       </c>
       <c r="E407" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H407">
         <v>5000</v>
@@ -16965,7 +16974,7 @@
         <v>6</v>
       </c>
       <c r="L407" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M407" s="2">
         <v>0.60416666666666696</v>
@@ -16987,7 +16996,7 @@
       </c>
       <c r="E408" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H408">
         <v>5000</v>
@@ -17002,7 +17011,7 @@
         <v>7</v>
       </c>
       <c r="L408" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M408" s="2">
         <v>0.60416666666666696</v>
@@ -17039,7 +17048,7 @@
         <v>8</v>
       </c>
       <c r="L409" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M409" s="2">
         <v>0.60416666666666696</v>
@@ -17061,7 +17070,7 @@
       </c>
       <c r="E410" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H410">
         <v>5000</v>
@@ -17076,7 +17085,7 @@
         <v>9</v>
       </c>
       <c r="L410" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M410" s="2">
         <v>0.60416666666666696</v>
@@ -17098,7 +17107,7 @@
       </c>
       <c r="E411" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H411">
         <v>5000</v>
@@ -17113,7 +17122,7 @@
         <v>10</v>
       </c>
       <c r="L411" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M411" s="2">
         <v>0.60416666666666696</v>
@@ -17135,7 +17144,7 @@
       </c>
       <c r="E412" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H412">
         <v>5000</v>
@@ -17150,7 +17159,7 @@
         <v>11</v>
       </c>
       <c r="L412" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M412" s="2">
         <v>0.60416666666666696</v>
@@ -17172,7 +17181,7 @@
       </c>
       <c r="E413" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H413">
         <v>5000</v>
@@ -17187,7 +17196,7 @@
         <v>12</v>
       </c>
       <c r="L413" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M413" s="2">
         <v>0.60416666666666696</v>
@@ -17224,7 +17233,7 @@
         <v>13</v>
       </c>
       <c r="L414" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M414" s="2">
         <v>0.60416666666666696</v>
@@ -17261,7 +17270,7 @@
         <v>14</v>
       </c>
       <c r="L415" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M415" s="2">
         <v>0.60416666666666696</v>
@@ -17283,7 +17292,7 @@
       </c>
       <c r="E416" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H416">
         <v>5000</v>
@@ -17298,7 +17307,7 @@
         <v>15</v>
       </c>
       <c r="L416" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M416" s="2">
         <v>0.60416666666666696</v>
@@ -17335,7 +17344,7 @@
         <v>1</v>
       </c>
       <c r="L417" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M417" s="2">
         <v>0.60416666666666696</v>
@@ -17357,7 +17366,7 @@
       </c>
       <c r="E418" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H418">
         <v>5000</v>
@@ -17372,7 +17381,7 @@
         <v>2</v>
       </c>
       <c r="L418" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M418" s="2">
         <v>0.60416666666666696</v>
@@ -17394,7 +17403,7 @@
       </c>
       <c r="E419" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H419">
         <v>5000</v>
@@ -17409,7 +17418,7 @@
         <v>3</v>
       </c>
       <c r="L419" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M419" s="2">
         <v>0.60416666666666696</v>
@@ -17431,7 +17440,7 @@
       </c>
       <c r="E420" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H420">
         <v>5000</v>
@@ -17446,7 +17455,7 @@
         <v>4</v>
       </c>
       <c r="L420" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M420" s="2">
         <v>0.60416666666666696</v>
@@ -17483,7 +17492,7 @@
         <v>5</v>
       </c>
       <c r="L421" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M421" s="2">
         <v>0.60416666666666696</v>
@@ -17520,7 +17529,7 @@
         <v>6</v>
       </c>
       <c r="L422" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M422" s="2">
         <v>0.60416666666666696</v>
@@ -17542,7 +17551,7 @@
       </c>
       <c r="E423" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H423">
         <v>5000</v>
@@ -17557,7 +17566,7 @@
         <v>7</v>
       </c>
       <c r="L423" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M423" s="2">
         <v>0.60416666666666696</v>
@@ -17594,7 +17603,7 @@
         <v>8</v>
       </c>
       <c r="L424" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="M424" s="2">
         <v>0.60416666666666696</v>
@@ -17616,7 +17625,7 @@
       </c>
       <c r="E425" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H425">
         <v>5000</v>
@@ -17631,7 +17640,7 @@
         <v>9</v>
       </c>
       <c r="L425" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M425" s="2">
         <v>0.60416666666666696</v>
@@ -17653,7 +17662,7 @@
       </c>
       <c r="E426" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H426">
         <v>5000</v>
@@ -17668,7 +17677,7 @@
         <v>10</v>
       </c>
       <c r="L426" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M426" s="2">
         <v>0.60416666666666696</v>
@@ -17705,7 +17714,7 @@
         <v>11</v>
       </c>
       <c r="L427" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M427" s="2">
         <v>0.60416666666666696</v>
@@ -17727,7 +17736,7 @@
       </c>
       <c r="E428" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H428">
         <v>5000</v>
@@ -17742,7 +17751,7 @@
         <v>12</v>
       </c>
       <c r="L428" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M428" s="2">
         <v>0.60416666666666696</v>
@@ -17764,7 +17773,7 @@
       </c>
       <c r="E429" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H429">
         <v>5000</v>
@@ -17779,7 +17788,7 @@
         <v>13</v>
       </c>
       <c r="L429" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M429" s="2">
         <v>0.60416666666666696</v>
@@ -17816,7 +17825,7 @@
         <v>14</v>
       </c>
       <c r="L430" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M430" s="2">
         <v>0.60416666666666696</v>
@@ -17838,7 +17847,7 @@
       </c>
       <c r="E431" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H431">
         <v>5000</v>
@@ -17853,7 +17862,7 @@
         <v>15</v>
       </c>
       <c r="L431" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="M431" s="2">
         <v>0.60416666666666696</v>
@@ -17875,7 +17884,7 @@
       </c>
       <c r="E432" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H432">
         <v>5000</v>
@@ -17890,7 +17899,7 @@
         <v>1</v>
       </c>
       <c r="L432" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M432" s="2">
         <v>0.60416666666666696</v>
@@ -17927,7 +17936,7 @@
         <v>2</v>
       </c>
       <c r="L433" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M433" s="2">
         <v>0.60416666666666696</v>
@@ -17949,7 +17958,7 @@
       </c>
       <c r="E434" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H434">
         <v>5000</v>
@@ -17964,7 +17973,7 @@
         <v>3</v>
       </c>
       <c r="L434" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="M434" s="2">
         <v>0.60416666666666696</v>
@@ -17986,7 +17995,7 @@
       </c>
       <c r="E435" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H435">
         <v>5000</v>
@@ -18001,7 +18010,7 @@
         <v>4</v>
       </c>
       <c r="L435" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M435" s="2">
         <v>0.60416666666666696</v>
@@ -18038,7 +18047,7 @@
         <v>5</v>
       </c>
       <c r="L436" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M436" s="2">
         <v>0.60416666666666696</v>
@@ -18075,7 +18084,7 @@
         <v>6</v>
       </c>
       <c r="L437" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M437" s="2">
         <v>0.60416666666666696</v>
@@ -18097,7 +18106,7 @@
       </c>
       <c r="E438" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H438">
         <v>5000</v>
@@ -18112,7 +18121,7 @@
         <v>7</v>
       </c>
       <c r="L438" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M438" s="2">
         <v>0.60416666666666696</v>
@@ -18149,7 +18158,7 @@
         <v>8</v>
       </c>
       <c r="L439" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M439" s="2">
         <v>0.60416666666666696</v>
@@ -18186,7 +18195,7 @@
         <v>9</v>
       </c>
       <c r="L440" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M440" s="2">
         <v>0.60416666666666696</v>
@@ -18223,7 +18232,7 @@
         <v>10</v>
       </c>
       <c r="L441" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="M441" s="2">
         <v>0.60416666666666696</v>
@@ -18245,7 +18254,7 @@
       </c>
       <c r="E442" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H442">
         <v>5000</v>
@@ -18260,7 +18269,7 @@
         <v>11</v>
       </c>
       <c r="L442" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M442" s="2">
         <v>0.60416666666666696</v>
@@ -18297,7 +18306,7 @@
         <v>12</v>
       </c>
       <c r="L443" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="M443" s="2">
         <v>0.60416666666666696</v>
@@ -18319,7 +18328,7 @@
       </c>
       <c r="E444" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H444">
         <v>5000</v>
@@ -18334,7 +18343,7 @@
         <v>13</v>
       </c>
       <c r="L444" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M444" s="2">
         <v>0.60416666666666696</v>
@@ -18356,7 +18365,7 @@
       </c>
       <c r="E445" t="str">
         <f t="shared" ca="1" si="12"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H445">
         <v>5000</v>
@@ -18371,7 +18380,7 @@
         <v>14</v>
       </c>
       <c r="L445" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M445" s="2">
         <v>0.60416666666666696</v>
@@ -18393,7 +18402,7 @@
       </c>
       <c r="E446" t="str">
         <f t="shared" ref="E446:E475" ca="1" si="14">IF(RAND()&gt;0.5, "남자", "여자")</f>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H446">
         <v>5000</v>
@@ -18408,7 +18417,7 @@
         <v>15</v>
       </c>
       <c r="L446" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M446" s="2">
         <v>0.60416666666666696</v>
@@ -18445,7 +18454,7 @@
         <v>1</v>
       </c>
       <c r="L447" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="M447" s="2">
         <v>0.60416666666666696</v>
@@ -18482,7 +18491,7 @@
         <v>2</v>
       </c>
       <c r="L448" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M448" s="2">
         <v>0.60416666666666696</v>
@@ -18504,7 +18513,7 @@
       </c>
       <c r="E449" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H449">
         <v>5000</v>
@@ -18519,7 +18528,7 @@
         <v>3</v>
       </c>
       <c r="L449" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M449" s="2">
         <v>0.60416666666666696</v>
@@ -18556,7 +18565,7 @@
         <v>4</v>
       </c>
       <c r="L450" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M450" s="2">
         <v>0.60416666666666696</v>
@@ -18578,7 +18587,7 @@
       </c>
       <c r="E451" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H451">
         <v>5000</v>
@@ -18593,7 +18602,7 @@
         <v>5</v>
       </c>
       <c r="L451" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M451" s="2">
         <v>0.60416666666666696</v>
@@ -18615,7 +18624,7 @@
       </c>
       <c r="E452" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H452">
         <v>5000</v>
@@ -18630,7 +18639,7 @@
         <v>6</v>
       </c>
       <c r="L452" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M452" s="2">
         <v>0.60416666666666696</v>
@@ -18667,7 +18676,7 @@
         <v>7</v>
       </c>
       <c r="L453" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M453" s="2">
         <v>0.60416666666666696</v>
@@ -18704,7 +18713,7 @@
         <v>8</v>
       </c>
       <c r="L454" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M454" s="2">
         <v>0.60416666666666696</v>
@@ -18726,7 +18735,7 @@
       </c>
       <c r="E455" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H455">
         <v>5000</v>
@@ -18741,7 +18750,7 @@
         <v>9</v>
       </c>
       <c r="L455" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M455" s="2">
         <v>0.60416666666666696</v>
@@ -18763,7 +18772,7 @@
       </c>
       <c r="E456" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H456">
         <v>5000</v>
@@ -18778,7 +18787,7 @@
         <v>10</v>
       </c>
       <c r="L456" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M456" s="2">
         <v>0.60416666666666696</v>
@@ -18815,7 +18824,7 @@
         <v>11</v>
       </c>
       <c r="L457" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M457" s="2">
         <v>0.60416666666666696</v>
@@ -18837,7 +18846,7 @@
       </c>
       <c r="E458" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H458">
         <v>5000</v>
@@ -18852,7 +18861,7 @@
         <v>12</v>
       </c>
       <c r="L458" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M458" s="2">
         <v>0.60416666666666696</v>
@@ -18874,7 +18883,7 @@
       </c>
       <c r="E459" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H459">
         <v>5000</v>
@@ -18889,7 +18898,7 @@
         <v>13</v>
       </c>
       <c r="L459" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M459" s="2">
         <v>0.60416666666666696</v>
@@ -18926,7 +18935,7 @@
         <v>14</v>
       </c>
       <c r="L460" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M460" s="2">
         <v>0.60416666666666696</v>
@@ -18963,7 +18972,7 @@
         <v>15</v>
       </c>
       <c r="L461" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="M461" s="2">
         <v>0.60416666666666696</v>
@@ -19000,7 +19009,7 @@
         <v>1</v>
       </c>
       <c r="L462" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M462" s="2">
         <v>0.60416666666666696</v>
@@ -19022,7 +19031,7 @@
       </c>
       <c r="E463" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H463">
         <v>5000</v>
@@ -19037,7 +19046,7 @@
         <v>2</v>
       </c>
       <c r="L463" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M463" s="2">
         <v>0.60416666666666696</v>
@@ -19059,7 +19068,7 @@
       </c>
       <c r="E464" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H464">
         <v>5000</v>
@@ -19074,7 +19083,7 @@
         <v>3</v>
       </c>
       <c r="L464" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="M464" s="2">
         <v>0.60416666666666696</v>
@@ -19096,7 +19105,7 @@
       </c>
       <c r="E465" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H465">
         <v>5000</v>
@@ -19111,7 +19120,7 @@
         <v>4</v>
       </c>
       <c r="L465" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M465" s="2">
         <v>0.60416666666666696</v>
@@ -19133,7 +19142,7 @@
       </c>
       <c r="E466" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H466">
         <v>5000</v>
@@ -19148,7 +19157,7 @@
         <v>5</v>
       </c>
       <c r="L466" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M466" s="2">
         <v>0.60416666666666696</v>
@@ -19185,7 +19194,7 @@
         <v>6</v>
       </c>
       <c r="L467" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M467" s="2">
         <v>0.60416666666666696</v>
@@ -19207,7 +19216,7 @@
       </c>
       <c r="E468" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H468">
         <v>5000</v>
@@ -19222,7 +19231,7 @@
         <v>7</v>
       </c>
       <c r="L468" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M468" s="2">
         <v>0.60416666666666696</v>
@@ -19244,7 +19253,7 @@
       </c>
       <c r="E469" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H469">
         <v>5000</v>
@@ -19259,7 +19268,7 @@
         <v>8</v>
       </c>
       <c r="L469" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M469" s="2">
         <v>0.60416666666666696</v>
@@ -19281,7 +19290,7 @@
       </c>
       <c r="E470" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H470">
         <v>5000</v>
@@ -19296,7 +19305,7 @@
         <v>9</v>
       </c>
       <c r="L470" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="M470" s="2">
         <v>0.60416666666666696</v>
@@ -19318,7 +19327,7 @@
       </c>
       <c r="E471" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H471">
         <v>5000</v>
@@ -19333,7 +19342,7 @@
         <v>10</v>
       </c>
       <c r="L471" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M471" s="2">
         <v>0.60416666666666696</v>
@@ -19370,7 +19379,7 @@
         <v>11</v>
       </c>
       <c r="L472" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M472" s="2">
         <v>0.60416666666666696</v>
@@ -19392,7 +19401,7 @@
       </c>
       <c r="E473" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H473">
         <v>5000</v>
@@ -19407,7 +19416,7 @@
         <v>12</v>
       </c>
       <c r="L473" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M473" s="2">
         <v>0.60416666666666696</v>
@@ -19429,7 +19438,7 @@
       </c>
       <c r="E474" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>여자</v>
+        <v>남자</v>
       </c>
       <c r="H474">
         <v>5000</v>
@@ -19444,7 +19453,7 @@
         <v>13</v>
       </c>
       <c r="L474" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M474" s="2">
         <v>0.60416666666666696</v>
@@ -19466,7 +19475,7 @@
       </c>
       <c r="E475" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>남자</v>
+        <v>여자</v>
       </c>
       <c r="H475">
         <v>5000</v>
@@ -19481,7 +19490,7 @@
         <v>14</v>
       </c>
       <c r="L475" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M475" s="2">
         <v>0.60416666666666696</v>
